--- a/Unity/Assets/Config/Excel/Datas/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/SkillConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22890" windowHeight="12600"/>
+    <workbookView windowWidth="22080" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="63">
   <si>
     <t>##var</t>
   </si>
@@ -60,6 +60,9 @@
     <t>Params</t>
   </si>
   <si>
+    <t>ActionEventId</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -97,6 +100,9 @@
   </si>
   <si>
     <t>技能参数</t>
+  </si>
+  <si>
+    <t>行为事件id</t>
   </si>
   <si>
     <t>扩散吞噬1级</t>
@@ -1257,7 +1263,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.7083333333333" style="4" customWidth="1"/>
@@ -1268,10 +1274,11 @@
     <col min="8" max="8" width="14.8583333333333" style="4" customWidth="1"/>
     <col min="9" max="9" width="12.5666666666667" style="4" customWidth="1"/>
     <col min="10" max="10" width="18.8583333333333" style="5" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="4"/>
+    <col min="11" max="11" width="12.5666666666667" style="4" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1302,72 +1309,81 @@
       <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="J2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" s="3" customFormat="1" spans="2:10">
+        <v>23</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" s="3" customFormat="1" spans="2:11">
       <c r="B4" s="3">
         <v>1001</v>
       </c>
@@ -1378,13 +1394,13 @@
         <v>2</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H4" s="3">
         <v>1000</v>
@@ -1393,10 +1409,13 @@
         <v>3000</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" s="3" customFormat="1" spans="2:10">
+        <v>27</v>
+      </c>
+      <c r="K4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" s="3" customFormat="1" spans="2:11">
       <c r="B5" s="3">
         <v>1001</v>
       </c>
@@ -1407,13 +1426,13 @@
         <v>2</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H5" s="3">
         <v>1000</v>
@@ -1422,10 +1441,13 @@
         <v>3000</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" s="3" customFormat="1" spans="2:10">
+        <v>30</v>
+      </c>
+      <c r="K5" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" spans="2:11">
       <c r="B6" s="3">
         <v>1001</v>
       </c>
@@ -1436,13 +1458,13 @@
         <v>2</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H6" s="3">
         <v>1000</v>
@@ -1451,10 +1473,13 @@
         <v>3000</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" s="3" customFormat="1" spans="2:10">
+        <v>33</v>
+      </c>
+      <c r="K6" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" s="3" customFormat="1" spans="2:11">
       <c r="B7" s="3">
         <v>1001</v>
       </c>
@@ -1465,13 +1490,13 @@
         <v>2</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H7" s="3">
         <v>1000</v>
@@ -1480,10 +1505,13 @@
         <v>3000</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10">
+        <v>36</v>
+      </c>
+      <c r="K7" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11">
       <c r="B8" s="3">
         <v>1002</v>
       </c>
@@ -1494,13 +1522,13 @@
         <v>2</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H8" s="3">
         <v>1000</v>
@@ -1509,10 +1537,13 @@
         <v>2000</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10">
+        <v>39</v>
+      </c>
+      <c r="K8" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11">
       <c r="B9" s="3">
         <v>1002</v>
       </c>
@@ -1523,13 +1554,13 @@
         <v>2</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H9" s="3">
         <v>1000</v>
@@ -1538,10 +1569,13 @@
         <v>2000</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10">
+        <v>42</v>
+      </c>
+      <c r="K9" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11">
       <c r="B10" s="3">
         <v>1002</v>
       </c>
@@ -1552,13 +1586,13 @@
         <v>2</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H10" s="3">
         <v>1000</v>
@@ -1567,10 +1601,13 @@
         <v>2000</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10">
+        <v>45</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11">
       <c r="B11" s="3">
         <v>1002</v>
       </c>
@@ -1581,13 +1618,13 @@
         <v>2</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H11" s="3">
         <v>1000</v>
@@ -1596,7 +1633,10 @@
         <v>2000</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
+      </c>
+      <c r="K11" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="10:10">
@@ -1631,7 +1671,7 @@
   <sheetData>
     <row r="4" spans="2:10">
       <c r="B4" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -1644,22 +1684,22 @@
     </row>
     <row r="5" spans="2:7">
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -1667,32 +1707,32 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="4:6">
       <c r="D7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="4:7">
       <c r="D8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/Datas/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/SkillConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22080" windowHeight="12180"/>
+    <workbookView windowWidth="22080" windowHeight="12180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="68">
   <si>
     <t>##var</t>
   </si>
@@ -57,142 +57,157 @@
     <t>CD</t>
   </si>
   <si>
+    <t>##Params</t>
+  </si>
+  <si>
+    <t>ActionEventIds</t>
+  </si>
+  <si>
+    <t>ActionEventTriggerPercent</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>(list#sep=,),int</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>技能等级</t>
+  </si>
+  <si>
+    <t>技能抽象类型</t>
+  </si>
+  <si>
+    <t>测试说明</t>
+  </si>
+  <si>
+    <t>名字</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>技能持续时间毫秒</t>
+  </si>
+  <si>
+    <t>冷却时间毫秒</t>
+  </si>
+  <si>
+    <t>技能参数</t>
+  </si>
+  <si>
+    <t>行为事件id</t>
+  </si>
+  <si>
+    <t>行为事件触发百分比，跟左边id一一对应</t>
+  </si>
+  <si>
+    <t>扩散吞噬1级</t>
+  </si>
+  <si>
+    <t>爆发混沌之力，吸食2m附近食物</t>
+  </si>
+  <si>
+    <t>0,1,2000</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>10,20</t>
+  </si>
+  <si>
+    <t>扩散吞噬2级</t>
+  </si>
+  <si>
+    <t>爆发混沌之力，吸食3m附近食物</t>
+  </si>
+  <si>
+    <t>0,1,3000</t>
+  </si>
+  <si>
+    <t>扩散吞噬3级</t>
+  </si>
+  <si>
+    <t>爆发混沌之力，吸食4m附近食物</t>
+  </si>
+  <si>
+    <t>0,1,4000</t>
+  </si>
+  <si>
+    <t>扩散吞噬4级</t>
+  </si>
+  <si>
+    <t>爆发混沌之力，吸食5m附近食物</t>
+  </si>
+  <si>
+    <t>0,1,5000</t>
+  </si>
+  <si>
+    <t>随机喷射1级</t>
+  </si>
+  <si>
+    <t>随机方向间隔发射1颗子弹</t>
+  </si>
+  <si>
+    <t>0,2,300,1500,1</t>
+  </si>
+  <si>
+    <t>随机喷射2级</t>
+  </si>
+  <si>
+    <t>随机方向间隔发射2颗子弹</t>
+  </si>
+  <si>
+    <t>0,2,300,1500,2</t>
+  </si>
+  <si>
+    <t>随机喷射3级</t>
+  </si>
+  <si>
+    <t>随机方向间隔发射3颗子弹</t>
+  </si>
+  <si>
+    <t>0,2,300,1500,3</t>
+  </si>
+  <si>
+    <t>随机喷射4级</t>
+  </si>
+  <si>
+    <t>随机方向间隔发射4颗子弹</t>
+  </si>
+  <si>
+    <t>0,2,300,1500,4</t>
+  </si>
+  <si>
+    <t>##技能数据来源可以来源编辑器，可自行开发TimeLine时间轴编辑不同技能数据</t>
+  </si>
+  <si>
+    <t>参数0</t>
+  </si>
+  <si>
+    <t>参数1</t>
+  </si>
+  <si>
+    <t>参数2</t>
+  </si>
+  <si>
+    <t>参数3</t>
+  </si>
+  <si>
+    <t>参数4</t>
+  </si>
+  <si>
     <t>Params</t>
-  </si>
-  <si>
-    <t>ActionEventId</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>(list#sep=,),int</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>技能等级</t>
-  </si>
-  <si>
-    <t>技能抽象类型</t>
-  </si>
-  <si>
-    <t>测试说明</t>
-  </si>
-  <si>
-    <t>名字</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>技能持续时间毫秒</t>
-  </si>
-  <si>
-    <t>冷却时间毫秒</t>
-  </si>
-  <si>
-    <t>技能参数</t>
-  </si>
-  <si>
-    <t>行为事件id</t>
-  </si>
-  <si>
-    <t>扩散吞噬1级</t>
-  </si>
-  <si>
-    <t>爆发混沌之力，吸食2m附近食物</t>
-  </si>
-  <si>
-    <t>0,1,2000</t>
-  </si>
-  <si>
-    <t>扩散吞噬2级</t>
-  </si>
-  <si>
-    <t>爆发混沌之力，吸食3m附近食物</t>
-  </si>
-  <si>
-    <t>0,1,3000</t>
-  </si>
-  <si>
-    <t>扩散吞噬3级</t>
-  </si>
-  <si>
-    <t>爆发混沌之力，吸食4m附近食物</t>
-  </si>
-  <si>
-    <t>0,1,4000</t>
-  </si>
-  <si>
-    <t>扩散吞噬4级</t>
-  </si>
-  <si>
-    <t>爆发混沌之力，吸食5m附近食物</t>
-  </si>
-  <si>
-    <t>0,1,5000</t>
-  </si>
-  <si>
-    <t>随机喷射1级</t>
-  </si>
-  <si>
-    <t>随机方向间隔发射1颗子弹</t>
-  </si>
-  <si>
-    <t>0,2,300,1500,1</t>
-  </si>
-  <si>
-    <t>随机喷射2级</t>
-  </si>
-  <si>
-    <t>随机方向间隔发射2颗子弹</t>
-  </si>
-  <si>
-    <t>0,2,300,1500,2</t>
-  </si>
-  <si>
-    <t>随机喷射3级</t>
-  </si>
-  <si>
-    <t>随机方向间隔发射3颗子弹</t>
-  </si>
-  <si>
-    <t>0,2,300,1500,3</t>
-  </si>
-  <si>
-    <t>随机喷射4级</t>
-  </si>
-  <si>
-    <t>随机方向间隔发射4颗子弹</t>
-  </si>
-  <si>
-    <t>0,2,300,1500,4</t>
-  </si>
-  <si>
-    <t>##技能数据来源可以来源编辑器，可自行开发TimeLine时间轴编辑不同技能数据</t>
-  </si>
-  <si>
-    <t>参数0</t>
-  </si>
-  <si>
-    <t>参数1</t>
-  </si>
-  <si>
-    <t>参数2</t>
-  </si>
-  <si>
-    <t>参数3</t>
-  </si>
-  <si>
-    <t>参数4</t>
   </si>
   <si>
     <t>触发时间点百分比</t>
@@ -931,49 +946,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>18775</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>18594</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="228600" y="2571750"/>
-          <a:ext cx="2522220" cy="3275965"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1263,7 +1235,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.7083333333333" style="4" customWidth="1"/>
@@ -1275,10 +1247,11 @@
     <col min="9" max="9" width="12.5666666666667" style="4" customWidth="1"/>
     <col min="10" max="10" width="18.8583333333333" style="5" customWidth="1"/>
     <col min="11" max="11" width="12.5666666666667" style="4" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="4"/>
+    <col min="12" max="12" width="27.5" style="4" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1312,78 +1285,87 @@
       <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="J2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>15</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" s="3" customFormat="1" spans="2:11">
+        <v>25</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" s="3" customFormat="1" spans="2:12">
       <c r="B4" s="3">
         <v>1001</v>
       </c>
@@ -1394,13 +1376,13 @@
         <v>2</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H4" s="3">
         <v>1000</v>
@@ -1409,13 +1391,16 @@
         <v>3000</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" s="3" customFormat="1" spans="2:11">
+        <v>29</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" s="3" customFormat="1" spans="2:12">
       <c r="B5" s="3">
         <v>1001</v>
       </c>
@@ -1426,13 +1411,13 @@
         <v>2</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H5" s="3">
         <v>1000</v>
@@ -1441,13 +1426,16 @@
         <v>3000</v>
       </c>
       <c r="J5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="K5" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" s="3" customFormat="1" spans="2:11">
+      <c r="L5" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" spans="2:12">
       <c r="B6" s="3">
         <v>1001</v>
       </c>
@@ -1458,13 +1446,13 @@
         <v>2</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H6" s="3">
         <v>1000</v>
@@ -1473,13 +1461,16 @@
         <v>3000</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="K6" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" s="3" customFormat="1" spans="2:11">
+        <v>37</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" s="3" customFormat="1" spans="2:12">
       <c r="B7" s="3">
         <v>1001</v>
       </c>
@@ -1490,13 +1481,13 @@
         <v>2</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H7" s="3">
         <v>1000</v>
@@ -1505,13 +1496,16 @@
         <v>3000</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="K7" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12">
       <c r="B8" s="3">
         <v>1002</v>
       </c>
@@ -1522,13 +1516,13 @@
         <v>2</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H8" s="3">
         <v>1000</v>
@@ -1537,13 +1531,16 @@
         <v>2000</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K8" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11">
+        <v>43</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12">
       <c r="B9" s="3">
         <v>1002</v>
       </c>
@@ -1554,13 +1551,13 @@
         <v>2</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H9" s="3">
         <v>1000</v>
@@ -1569,13 +1566,16 @@
         <v>2000</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="K9" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11">
+        <v>46</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12">
       <c r="B10" s="3">
         <v>1002</v>
       </c>
@@ -1586,13 +1586,13 @@
         <v>2</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H10" s="3">
         <v>1000</v>
@@ -1601,13 +1601,16 @@
         <v>2000</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="K10" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11">
+        <v>49</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12">
       <c r="B11" s="3">
         <v>1002</v>
       </c>
@@ -1618,13 +1621,13 @@
         <v>2</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H11" s="3">
         <v>1000</v>
@@ -1633,10 +1636,13 @@
         <v>2000</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="K11" s="3">
-        <v>2</v>
+        <v>52</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="10:10">
@@ -1671,7 +1677,7 @@
   <sheetData>
     <row r="4" spans="2:10">
       <c r="B4" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -1684,61 +1690,60 @@
     </row>
     <row r="5" spans="2:7">
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="B6" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="4:6">
       <c r="D7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="4:7">
       <c r="D8" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G8" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/Datas/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/SkillConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22080" windowHeight="12180" activeTab="1"/>
+    <workbookView windowWidth="23355" windowHeight="12570"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="67">
   <si>
     <t>##var</t>
   </si>
@@ -118,9 +118,6 @@
   </si>
   <si>
     <t>0,1,2000</t>
-  </si>
-  <si>
-    <t>1,2</t>
   </si>
   <si>
     <t>10,20</t>
@@ -1393,11 +1390,11 @@
       <c r="J4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="3">
+        <v>1</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="5" s="3" customFormat="1" spans="2:12">
@@ -1414,10 +1411,10 @@
         <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>32</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>33</v>
       </c>
       <c r="H5" s="3">
         <v>1000</v>
@@ -1426,13 +1423,13 @@
         <v>3000</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="K5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" s="3">
+        <v>1</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" spans="2:12">
@@ -1449,10 +1446,10 @@
         <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>35</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>36</v>
       </c>
       <c r="H6" s="3">
         <v>1000</v>
@@ -1461,13 +1458,13 @@
         <v>3000</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="K6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" s="3">
+        <v>1</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="7" s="3" customFormat="1" spans="2:12">
@@ -1484,10 +1481,10 @@
         <v>19</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>38</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>39</v>
       </c>
       <c r="H7" s="3">
         <v>1000</v>
@@ -1496,13 +1493,13 @@
         <v>3000</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="K7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="3">
+        <v>1</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="8" spans="2:12">
@@ -1519,10 +1516,10 @@
         <v>19</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>42</v>
       </c>
       <c r="H8" s="3">
         <v>1000</v>
@@ -1531,13 +1528,13 @@
         <v>2000</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="K8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" s="3">
+        <v>2</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="9" spans="2:12">
@@ -1554,10 +1551,10 @@
         <v>19</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>45</v>
       </c>
       <c r="H9" s="3">
         <v>1000</v>
@@ -1566,13 +1563,13 @@
         <v>2000</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="K9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="3">
+        <v>2</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="10" spans="2:12">
@@ -1589,10 +1586,10 @@
         <v>19</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>48</v>
       </c>
       <c r="H10" s="3">
         <v>1000</v>
@@ -1601,13 +1598,13 @@
         <v>2000</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="K10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="11" spans="2:12">
@@ -1624,10 +1621,10 @@
         <v>19</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>50</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>51</v>
       </c>
       <c r="H11" s="3">
         <v>1000</v>
@@ -1636,13 +1633,13 @@
         <v>2000</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="K11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K11" s="3">
+        <v>2</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="12" spans="10:10">
@@ -1677,7 +1674,7 @@
   <sheetData>
     <row r="4" spans="2:10">
       <c r="B4" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -1693,52 +1690,52 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" t="s">
         <v>54</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>55</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>56</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>57</v>
-      </c>
-      <c r="G5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="B6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" t="s">
         <v>59</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>60</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>61</v>
-      </c>
-      <c r="E6" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="7" spans="4:6">
       <c r="D7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" t="s">
         <v>63</v>
-      </c>
-      <c r="F7" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="8" spans="4:7">
       <c r="D8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" t="s">
         <v>65</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>66</v>
-      </c>
-      <c r="G8" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/Datas/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/SkillConfig.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
     <sheet name="#说明" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>##var</t>
   </si>
@@ -118,9 +118,6 @@
   </si>
   <si>
     <t>0,1,2000</t>
-  </si>
-  <si>
-    <t>10,20</t>
   </si>
   <si>
     <t>扩散吞噬2级</t>
@@ -724,164 +721,164 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="49">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1230,25 +1227,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <sheetPr/>
   <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="12.7083333333333" style="4" customWidth="1"/>
-    <col min="2" max="4" width="12.5666666666667" style="4" customWidth="1"/>
-    <col min="5" max="5" width="15.1416666666667" style="4" customWidth="1"/>
-    <col min="6" max="6" width="13.5666666666667" style="4" customWidth="1"/>
-    <col min="7" max="7" width="28.7083333333333" style="4" customWidth="1"/>
-    <col min="8" max="8" width="14.8583333333333" style="4" customWidth="1"/>
-    <col min="9" max="9" width="12.5666666666667" style="4" customWidth="1"/>
-    <col min="10" max="10" width="18.8583333333333" style="5" customWidth="1"/>
-    <col min="11" max="11" width="12.5666666666667" style="4" customWidth="1"/>
-    <col min="12" max="12" width="27.5" style="4" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="12.7083333333333" customWidth="1" style="4"/>
+    <col min="2" max="4" width="12.5666666666667" customWidth="1" style="4"/>
+    <col min="5" max="5" width="15.1416666666667" customWidth="1" style="4"/>
+    <col min="6" max="6" width="13.5666666666667" customWidth="1" style="4"/>
+    <col min="7" max="7" width="28.7083333333333" customWidth="1" style="4"/>
+    <col min="8" max="8" width="14.8583333333333" customWidth="1" style="4"/>
+    <col min="9" max="9" width="12.5666666666667" customWidth="1" style="4"/>
+    <col min="10" max="10" width="18.8583333333333" customWidth="1" style="5"/>
+    <col min="11" max="11" width="12.5666666666667" customWidth="1" style="4"/>
+    <col min="12" max="12" width="27.5" customWidth="1" style="4"/>
+    <col min="13" max="16384" width="9" customWidth="1" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1286,7 +1283,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
@@ -1324,7 +1321,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3">
       <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
@@ -1362,7 +1359,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" s="3" customFormat="1" spans="2:12">
+    <row r="4" s="3" customFormat="1">
       <c r="B4" s="3">
         <v>1001</v>
       </c>
@@ -1393,11 +1390,11 @@
       <c r="K4" s="3">
         <v>1</v>
       </c>
-      <c r="L4" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" s="3" customFormat="1" spans="2:12">
+      <c r="L4" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" s="3" customFormat="1">
       <c r="B5" s="3">
         <v>1001</v>
       </c>
@@ -1411,10 +1408,10 @@
         <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>31</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="H5" s="3">
         <v>1000</v>
@@ -1423,16 +1420,16 @@
         <v>3000</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K5" s="3">
         <v>1</v>
       </c>
-      <c r="L5" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" s="3" customFormat="1" spans="2:12">
+      <c r="L5" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1">
       <c r="B6" s="3">
         <v>1001</v>
       </c>
@@ -1446,10 +1443,10 @@
         <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="H6" s="3">
         <v>1000</v>
@@ -1458,16 +1455,16 @@
         <v>3000</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K6" s="3">
         <v>1</v>
       </c>
-      <c r="L6" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" s="3" customFormat="1" spans="2:12">
+      <c r="L6" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" s="3" customFormat="1">
       <c r="B7" s="3">
         <v>1001</v>
       </c>
@@ -1481,10 +1478,10 @@
         <v>19</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>38</v>
       </c>
       <c r="H7" s="3">
         <v>1000</v>
@@ -1493,16 +1490,16 @@
         <v>3000</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K7" s="3">
         <v>1</v>
       </c>
-      <c r="L7" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12">
+      <c r="L7" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="B8" s="3">
         <v>1002</v>
       </c>
@@ -1516,10 +1513,10 @@
         <v>19</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="H8" s="3">
         <v>1000</v>
@@ -1528,16 +1525,16 @@
         <v>2000</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K8" s="3">
-        <v>2</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12">
+        <v>5</v>
+      </c>
+      <c r="L8" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="3">
         <v>1002</v>
       </c>
@@ -1551,10 +1548,10 @@
         <v>19</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>44</v>
       </c>
       <c r="H9" s="3">
         <v>1000</v>
@@ -1563,16 +1560,16 @@
         <v>2000</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K9" s="3">
-        <v>2</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12">
+        <v>6</v>
+      </c>
+      <c r="L9" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="B10" s="3">
         <v>1002</v>
       </c>
@@ -1586,10 +1583,10 @@
         <v>19</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="H10" s="3">
         <v>1000</v>
@@ -1598,16 +1595,16 @@
         <v>2000</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K10" s="3">
-        <v>2</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12">
+        <v>7</v>
+      </c>
+      <c r="L10" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="B11" s="3">
         <v>1002</v>
       </c>
@@ -1621,10 +1618,10 @@
         <v>19</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>49</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>50</v>
       </c>
       <c r="H11" s="3">
         <v>1000</v>
@@ -1633,25 +1630,25 @@
         <v>2000</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K11" s="3">
-        <v>2</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="10:10">
+        <v>8</v>
+      </c>
+      <c r="L11" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="10:10">
+    <row r="13">
       <c r="J13" s="9"/>
     </row>
-    <row r="14" spans="10:10">
+    <row r="14">
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="10:10">
+    <row r="15">
       <c r="J15" s="9"/>
     </row>
   </sheetData>
@@ -1662,7 +1659,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <sheetPr/>
   <dimension ref="B4:J8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
@@ -1672,9 +1669,9 @@
     <col min="6" max="6" width="18.7083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:10">
+    <row r="4">
       <c r="B4" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -1685,57 +1682,57 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="2:7">
-      <c r="B5" t="s">
+    <row r="5">
+      <c r="B5" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="G5" t="s">
+    </row>
+    <row r="6">
+      <c r="B6" s="0" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="6" spans="2:5">
-      <c r="B6" t="s">
+      <c r="C6" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="E6" t="s">
+    </row>
+    <row r="7">
+      <c r="D7" s="0" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="7" spans="4:6">
-      <c r="D7" t="s">
+      <c r="F7" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="F7" t="s">
+    </row>
+    <row r="8">
+      <c r="D8" s="0" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="8" spans="4:7">
-      <c r="D8" t="s">
+      <c r="F8" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" s="0" t="s">
         <v>65</v>
-      </c>
-      <c r="G8" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
